--- a/VerveStacks_PHL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_PHL_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_PHL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{952A6A4A-EFB0-4ABE-89CF-EF1F136E39D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC8E0663-33CD-4069-A818-224429710579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5824,7 +5824,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17CD101-2F7C-4D0C-BCFF-9A051E329F85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{536324F5-DEA8-44CE-8141-251063FEBB03}">
   <dimension ref="B2:AF883"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27893,7 +27893,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB26EF24-D0AE-4533-81FA-31E9D4D1F108}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE928AD-2722-48C4-BBAE-1D8E8FD5BB94}">
   <dimension ref="B9:L114"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
